--- a/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0003T0006Z000C1N68_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0003T0006Z000C1N68_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>19.63516109197067</v>
+        <v>3.190713677445234</v>
       </c>
       <c r="D2" t="n">
-        <v>32.01682620894562</v>
+        <v>5.202734258953662</v>
       </c>
       <c r="E2" t="n">
-        <v>11.96179640620744</v>
+        <v>1.943791916008709</v>
       </c>
       <c r="F2" t="n">
-        <v>12.11667526732899</v>
+        <v>1.968959730940961</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>8.855224255094249</v>
+        <v>1.438973941452816</v>
       </c>
       <c r="D3" t="n">
-        <v>8.527538244983193</v>
+        <v>1.385724964809769</v>
       </c>
       <c r="E3" t="n">
-        <v>11.96179640620744</v>
+        <v>1.943791916008709</v>
       </c>
       <c r="F3" t="n">
-        <v>12.11667526732899</v>
+        <v>1.968959730940961</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>37.8021163428716</v>
+        <v>6.142843905716635</v>
       </c>
       <c r="D4" t="n">
-        <v>11.6619037896906</v>
+        <v>1.895059365824723</v>
       </c>
       <c r="E4" t="n">
-        <v>11.96179640620744</v>
+        <v>1.943791916008709</v>
       </c>
       <c r="F4" t="n">
-        <v>12.11667526732899</v>
+        <v>1.968959730940961</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>18.67999039992205</v>
+        <v>3.035498439987333</v>
       </c>
       <c r="D5" t="n">
-        <v>8.325576443172634</v>
+        <v>1.352906172015553</v>
       </c>
       <c r="E5" t="n">
-        <v>11.96179640620744</v>
+        <v>1.943791916008709</v>
       </c>
       <c r="F5" t="n">
-        <v>12.11667526732899</v>
+        <v>1.968959730940961</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>2.540535050487904</v>
+        <v>0.4128369457042845</v>
       </c>
       <c r="D6" t="n">
-        <v>28.79863036866704</v>
+        <v>4.679777434908393</v>
       </c>
       <c r="E6" t="n">
-        <v>11.96179640620744</v>
+        <v>1.943791916008709</v>
       </c>
       <c r="F6" t="n">
-        <v>12.11667526732899</v>
+        <v>1.968959730940961</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>8.610128391002609</v>
+        <v>1.399145863537924</v>
       </c>
       <c r="D7" t="n">
-        <v>15.2638475678053</v>
+        <v>2.480375229768361</v>
       </c>
       <c r="E7" t="n">
-        <v>11.96179640620744</v>
+        <v>1.943791916008709</v>
       </c>
       <c r="F7" t="n">
-        <v>12.11667526732899</v>
+        <v>1.968959730940961</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>22.51676128469507</v>
+        <v>3.658973708762949</v>
       </c>
       <c r="D8" t="n">
-        <v>25.48688629157172</v>
+        <v>4.141619022380405</v>
       </c>
       <c r="E8" t="n">
-        <v>11.96179640620744</v>
+        <v>1.943791916008709</v>
       </c>
       <c r="F8" t="n">
-        <v>12.11667526732899</v>
+        <v>1.968959730940961</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>23.40703091692562</v>
+        <v>3.803642524000414</v>
       </c>
       <c r="D9" t="n">
-        <v>45.73624869230579</v>
+        <v>7.432140412499692</v>
       </c>
       <c r="E9" t="n">
-        <v>11.96179640620744</v>
+        <v>1.943791916008709</v>
       </c>
       <c r="F9" t="n">
-        <v>12.11667526732899</v>
+        <v>1.968959730940961</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>25.82172179221128</v>
+        <v>4.196029791234333</v>
       </c>
       <c r="D10" t="n">
-        <v>34.48832330578633</v>
+        <v>5.604352537190279</v>
       </c>
       <c r="E10" t="n">
-        <v>11.96179640620744</v>
+        <v>1.943791916008709</v>
       </c>
       <c r="F10" t="n">
-        <v>12.11667526732899</v>
+        <v>1.968959730940961</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>24.78655945954336</v>
+        <v>4.027815912175797</v>
       </c>
       <c r="D11" t="n">
-        <v>22.20014030907836</v>
+        <v>3.607522800225234</v>
       </c>
       <c r="E11" t="n">
-        <v>11.96179640620744</v>
+        <v>1.943791916008709</v>
       </c>
       <c r="F11" t="n">
-        <v>12.11667526732899</v>
+        <v>1.968959730940961</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>10.30776406404415</v>
+        <v>1.675011660407175</v>
       </c>
       <c r="D12" t="n">
-        <v>13.64734406395618</v>
+        <v>2.217693410392879</v>
       </c>
       <c r="E12" t="n">
-        <v>11.96179640620744</v>
+        <v>1.943791916008709</v>
       </c>
       <c r="F12" t="n">
-        <v>12.11667526732899</v>
+        <v>1.968959730940961</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>28.60069929215018</v>
+        <v>4.647613634974404</v>
       </c>
       <c r="D13" t="n">
-        <v>12.30739528423438</v>
+        <v>1.999951733688086</v>
       </c>
       <c r="E13" t="n">
-        <v>11.96179640620744</v>
+        <v>1.943791916008709</v>
       </c>
       <c r="F13" t="n">
-        <v>12.11667526732899</v>
+        <v>1.968959730940961</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>40.97737921866052</v>
+        <v>6.658824123032336</v>
       </c>
       <c r="D14" t="n">
-        <v>30.48038745547831</v>
+        <v>4.953062961515225</v>
       </c>
       <c r="E14" t="n">
-        <v>11.96179640620744</v>
+        <v>1.943791916008709</v>
       </c>
       <c r="F14" t="n">
-        <v>12.11667526732899</v>
+        <v>1.968959730940961</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>32.8685967991355</v>
+        <v>5.341146979859519</v>
       </c>
       <c r="D15" t="n">
-        <v>25.24671154191337</v>
+        <v>4.102590625560922</v>
       </c>
       <c r="E15" t="n">
-        <v>11.96179640620744</v>
+        <v>1.943791916008709</v>
       </c>
       <c r="F15" t="n">
-        <v>12.11667526732899</v>
+        <v>1.968959730940961</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>15.14090494421898</v>
+        <v>2.460397053435583</v>
       </c>
       <c r="D16" t="n">
-        <v>31.76446751117982</v>
+        <v>5.16172597056672</v>
       </c>
       <c r="E16" t="n">
-        <v>11.96179640620744</v>
+        <v>1.943791916008709</v>
       </c>
       <c r="F16" t="n">
-        <v>12.11667526732899</v>
+        <v>1.968959730940961</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>28.38848140690715</v>
+        <v>4.613128228622412</v>
       </c>
       <c r="D17" t="n">
-        <v>39.81519810323691</v>
+        <v>6.469969691775998</v>
       </c>
       <c r="E17" t="n">
-        <v>11.96179640620744</v>
+        <v>1.943791916008709</v>
       </c>
       <c r="F17" t="n">
-        <v>12.11667526732899</v>
+        <v>1.968959730940961</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>47.56830663915505</v>
+        <v>7.729849828862696</v>
       </c>
       <c r="D18" t="n">
-        <v>45.41200281863816</v>
+        <v>7.379450458028701</v>
       </c>
       <c r="E18" t="n">
-        <v>11.96179640620744</v>
+        <v>1.943791916008709</v>
       </c>
       <c r="F18" t="n">
-        <v>12.11667526732899</v>
+        <v>1.968959730940961</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>37.26269528642515</v>
+        <v>6.055187984044087</v>
       </c>
       <c r="D19" t="n">
-        <v>40.93763401797538</v>
+        <v>6.652365527920999</v>
       </c>
       <c r="E19" t="n">
-        <v>11.96179640620744</v>
+        <v>1.943791916008709</v>
       </c>
       <c r="F19" t="n">
-        <v>12.11667526732899</v>
+        <v>1.968959730940961</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
